--- a/100_easy_leetcode.xlsx
+++ b/100_easy_leetcode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vises\OneDrive\Desktop\Python_programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784A2280-AE6C-41F4-841E-93AFF9AF58B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7741AAF-0840-45F5-9F7C-65A107F4CCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="198">
   <si>
     <t>No.</t>
   </si>
@@ -608,6 +608,12 @@
   </si>
   <si>
     <t>https://leetcode.com/problems/partition-labels/</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Revision No:</t>
   </si>
 </sst>
 </file>
@@ -646,7 +652,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -669,6 +675,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -677,12 +694,15 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -988,15 +1008,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="69.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1009,8 +1031,14 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1024,7 +1052,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1038,7 +1066,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1052,7 +1080,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1066,7 +1094,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1080,7 +1108,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1094,7 +1122,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1108,7 +1136,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1122,7 +1150,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1136,7 +1164,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1150,7 +1178,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1164,7 +1192,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1178,7 +1206,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1192,7 +1220,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1206,7 +1234,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>

--- a/100_easy_leetcode.xlsx
+++ b/100_easy_leetcode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vises\OneDrive\Desktop\Python_programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7741AAF-0840-45F5-9F7C-65A107F4CCD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EB2C06-E724-43A4-B2E1-582BF4E6F41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="199">
   <si>
     <t>No.</t>
   </si>
@@ -614,6 +614,9 @@
   </si>
   <si>
     <t>Revision No:</t>
+  </si>
+  <si>
+    <t>YES</t>
   </si>
 </sst>
 </file>
@@ -700,7 +703,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1051,6 +1054,9 @@
       <c r="D2" s="2" t="s">
         <v>106</v>
       </c>
+      <c r="E2" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -1065,6 +1071,9 @@
       <c r="D3" s="2" t="s">
         <v>107</v>
       </c>
+      <c r="E3" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
@@ -1078,6 +1087,9 @@
       </c>
       <c r="D4" s="2" t="s">
         <v>108</v>
+      </c>
+      <c r="E4" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">

--- a/100_easy_leetcode.xlsx
+++ b/100_easy_leetcode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vises\OneDrive\Desktop\Python_programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EB2C06-E724-43A4-B2E1-582BF4E6F41D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4783FA1B-9AB4-4751-B82E-E4221452F336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="291">
   <si>
     <t>No.</t>
   </si>
@@ -617,6 +617,282 @@
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t>LC1</t>
+  </si>
+  <si>
+    <t>LC121</t>
+  </si>
+  <si>
+    <t>LC26</t>
+  </si>
+  <si>
+    <t>LC217</t>
+  </si>
+  <si>
+    <t>LC136</t>
+  </si>
+  <si>
+    <t>LC350</t>
+  </si>
+  <si>
+    <t>LC66</t>
+  </si>
+  <si>
+    <t>LC283</t>
+  </si>
+  <si>
+    <t>LC169</t>
+  </si>
+  <si>
+    <t>LC189</t>
+  </si>
+  <si>
+    <t>LC242</t>
+  </si>
+  <si>
+    <t>LC20</t>
+  </si>
+  <si>
+    <t>LC387</t>
+  </si>
+  <si>
+    <t>LC344</t>
+  </si>
+  <si>
+    <t>LC7</t>
+  </si>
+  <si>
+    <t>LC9</t>
+  </si>
+  <si>
+    <t>LC28</t>
+  </si>
+  <si>
+    <t>LC14</t>
+  </si>
+  <si>
+    <t>LC67</t>
+  </si>
+  <si>
+    <t>LC38</t>
+  </si>
+  <si>
+    <t>LC21</t>
+  </si>
+  <si>
+    <t>LC206</t>
+  </si>
+  <si>
+    <t>LC141</t>
+  </si>
+  <si>
+    <t>LC203</t>
+  </si>
+  <si>
+    <t>LC234</t>
+  </si>
+  <si>
+    <t>LC160</t>
+  </si>
+  <si>
+    <t>LC237</t>
+  </si>
+  <si>
+    <t>LC876</t>
+  </si>
+  <si>
+    <t>LC1290</t>
+  </si>
+  <si>
+    <t>LC83</t>
+  </si>
+  <si>
+    <t>LC104</t>
+  </si>
+  <si>
+    <t>LC101</t>
+  </si>
+  <si>
+    <t>LC226</t>
+  </si>
+  <si>
+    <t>LC112</t>
+  </si>
+  <si>
+    <t>LC110</t>
+  </si>
+  <si>
+    <t>LC257</t>
+  </si>
+  <si>
+    <t>LC100</t>
+  </si>
+  <si>
+    <t>LC94</t>
+  </si>
+  <si>
+    <t>LC111</t>
+  </si>
+  <si>
+    <t>LC108</t>
+  </si>
+  <si>
+    <t>LC70</t>
+  </si>
+  <si>
+    <t>LC53</t>
+  </si>
+  <si>
+    <t>LC198</t>
+  </si>
+  <si>
+    <t>LC746</t>
+  </si>
+  <si>
+    <t>LC509</t>
+  </si>
+  <si>
+    <t>LC118</t>
+  </si>
+  <si>
+    <t>LC62</t>
+  </si>
+  <si>
+    <t>LC122</t>
+  </si>
+  <si>
+    <t>LC1137</t>
+  </si>
+  <si>
+    <t>LC322</t>
+  </si>
+  <si>
+    <t>LC461</t>
+  </si>
+  <si>
+    <t>LC191</t>
+  </si>
+  <si>
+    <t>LC342</t>
+  </si>
+  <si>
+    <t>LC190</t>
+  </si>
+  <si>
+    <t>LC258</t>
+  </si>
+  <si>
+    <t>LC231</t>
+  </si>
+  <si>
+    <t>LC13</t>
+  </si>
+  <si>
+    <t>LC412</t>
+  </si>
+  <si>
+    <t>LC171</t>
+  </si>
+  <si>
+    <t>LC704</t>
+  </si>
+  <si>
+    <t>LC349</t>
+  </si>
+  <si>
+    <t>LC374</t>
+  </si>
+  <si>
+    <t>LC278</t>
+  </si>
+  <si>
+    <t>LC162</t>
+  </si>
+  <si>
+    <t>LC709</t>
+  </si>
+  <si>
+    <t>LC657</t>
+  </si>
+  <si>
+    <t>LC938</t>
+  </si>
+  <si>
+    <t>LC872</t>
+  </si>
+  <si>
+    <t>LC766</t>
+  </si>
+  <si>
+    <t>LC867</t>
+  </si>
+  <si>
+    <t>LC832</t>
+  </si>
+  <si>
+    <t>LC566</t>
+  </si>
+  <si>
+    <t>LC728</t>
+  </si>
+  <si>
+    <t>LC125</t>
+  </si>
+  <si>
+    <t>LC151</t>
+  </si>
+  <si>
+    <t>LC172</t>
+  </si>
+  <si>
+    <t>LC371</t>
+  </si>
+  <si>
+    <t>LC209</t>
+  </si>
+  <si>
+    <t>LC3</t>
+  </si>
+  <si>
+    <t>LC438</t>
+  </si>
+  <si>
+    <t>LC567</t>
+  </si>
+  <si>
+    <t>LC30</t>
+  </si>
+  <si>
+    <t>LC11</t>
+  </si>
+  <si>
+    <t>LC15</t>
+  </si>
+  <si>
+    <t>LC680</t>
+  </si>
+  <si>
+    <t>LC455</t>
+  </si>
+  <si>
+    <t>LC55</t>
+  </si>
+  <si>
+    <t>LC134</t>
+  </si>
+  <si>
+    <t>LC135</t>
+  </si>
+  <si>
+    <t>LC763</t>
+  </si>
+  <si>
+    <t>LEVEL</t>
+  </si>
+  <si>
+    <t>EASY</t>
   </si>
 </sst>
 </file>
@@ -697,7 +973,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -706,6 +982,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1011,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
@@ -1021,7 +1302,7 @@
     <col min="6" max="6" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1040,10 +1321,13 @@
       <c r="F1" s="3" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
+      <c r="G1" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -1057,10 +1341,13 @@
       <c r="E2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
+      <c r="G2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>200</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -1074,10 +1361,13 @@
       <c r="E3" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
+      <c r="G3" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
@@ -1091,10 +1381,13 @@
       <c r="E4" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
+      <c r="G4" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>202</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
@@ -1105,10 +1398,13 @@
       <c r="D5" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
+      <c r="G5" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>203</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -1119,10 +1415,13 @@
       <c r="D6" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
+      <c r="G6" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>204</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -1133,10 +1432,13 @@
       <c r="D7" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
+      <c r="G7" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>205</v>
       </c>
       <c r="B8" t="s">
         <v>4</v>
@@ -1147,10 +1449,13 @@
       <c r="D8" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
+      <c r="G8" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="B9" t="s">
         <v>4</v>
@@ -1161,10 +1466,13 @@
       <c r="D9" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
+      <c r="G9" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -1175,10 +1483,13 @@
       <c r="D10" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
+      <c r="G10" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>208</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -1189,10 +1500,13 @@
       <c r="D11" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
+      <c r="G11" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>209</v>
       </c>
       <c r="B12" t="s">
         <v>4</v>
@@ -1203,10 +1517,13 @@
       <c r="D12" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
+      <c r="G12" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="B13" t="s">
         <v>4</v>
@@ -1217,10 +1534,13 @@
       <c r="D13" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
+      <c r="G13" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="B14" t="s">
         <v>4</v>
@@ -1231,10 +1551,13 @@
       <c r="D14" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
+      <c r="G14" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -1245,10 +1568,13 @@
       <c r="D15" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>15</v>
+      <c r="G15" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>213</v>
       </c>
       <c r="B16" t="s">
         <v>4</v>
@@ -1259,10 +1585,13 @@
       <c r="D16" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
+      <c r="G16" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="B17" t="s">
         <v>4</v>
@@ -1273,10 +1602,13 @@
       <c r="D17" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>17</v>
+      <c r="G17" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="B18" t="s">
         <v>4</v>
@@ -1287,10 +1619,13 @@
       <c r="D18" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>18</v>
+      <c r="G18" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="B19" t="s">
         <v>4</v>
@@ -1301,10 +1636,13 @@
       <c r="D19" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>19</v>
+      <c r="G19" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="B20" t="s">
         <v>4</v>
@@ -1315,10 +1653,13 @@
       <c r="D20" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>20</v>
+      <c r="G20" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="B21" t="s">
         <v>4</v>
@@ -1329,10 +1670,13 @@
       <c r="D21" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>21</v>
+      <c r="G21" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>219</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
@@ -1343,10 +1687,13 @@
       <c r="D22" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>22</v>
+      <c r="G22" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
@@ -1357,10 +1704,13 @@
       <c r="D23" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>23</v>
+      <c r="G23" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
@@ -1371,10 +1721,13 @@
       <c r="D24" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>24</v>
+      <c r="G24" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
+        <v>222</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
@@ -1385,10 +1738,13 @@
       <c r="D25" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>25</v>
+      <c r="G25" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
@@ -1399,10 +1755,13 @@
       <c r="D26" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>26</v>
+      <c r="G26" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
@@ -1413,10 +1772,13 @@
       <c r="D27" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>27</v>
+      <c r="G27" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="5" t="s">
+        <v>225</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
@@ -1427,10 +1789,13 @@
       <c r="D28" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>28</v>
+      <c r="G28" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="B29" t="s">
         <v>5</v>
@@ -1441,10 +1806,13 @@
       <c r="D29" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>29</v>
+      <c r="G29" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="B30" t="s">
         <v>5</v>
@@ -1455,10 +1823,13 @@
       <c r="D30" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>30</v>
+      <c r="G30" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>228</v>
       </c>
       <c r="B31" t="s">
         <v>5</v>
@@ -1469,10 +1840,13 @@
       <c r="D31" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>31</v>
+      <c r="G31" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>229</v>
       </c>
       <c r="B32" t="s">
         <v>6</v>
@@ -1483,10 +1857,13 @@
       <c r="D32" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>32</v>
+      <c r="G32" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>230</v>
       </c>
       <c r="B33" t="s">
         <v>6</v>
@@ -1497,10 +1874,13 @@
       <c r="D33" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>33</v>
+      <c r="G33" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>231</v>
       </c>
       <c r="B34" t="s">
         <v>6</v>
@@ -1511,10 +1891,13 @@
       <c r="D34" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>34</v>
+      <c r="G34" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>232</v>
       </c>
       <c r="B35" t="s">
         <v>6</v>
@@ -1525,10 +1908,13 @@
       <c r="D35" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>35</v>
+      <c r="G35" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>233</v>
       </c>
       <c r="B36" t="s">
         <v>6</v>
@@ -1539,10 +1925,13 @@
       <c r="D36" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>36</v>
+      <c r="G36" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="6" t="s">
+        <v>234</v>
       </c>
       <c r="B37" t="s">
         <v>6</v>
@@ -1553,10 +1942,13 @@
       <c r="D37" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>37</v>
+      <c r="G37" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="6" t="s">
+        <v>235</v>
       </c>
       <c r="B38" t="s">
         <v>6</v>
@@ -1567,10 +1959,13 @@
       <c r="D38" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>38</v>
+      <c r="G38" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="6" t="s">
+        <v>236</v>
       </c>
       <c r="B39" t="s">
         <v>6</v>
@@ -1581,10 +1976,13 @@
       <c r="D39" s="2" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>39</v>
+      <c r="G39" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="s">
+        <v>237</v>
       </c>
       <c r="B40" t="s">
         <v>6</v>
@@ -1595,10 +1993,13 @@
       <c r="D40" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>40</v>
+      <c r="G40" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="s">
+        <v>238</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
@@ -1609,10 +2010,13 @@
       <c r="D41" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>41</v>
+      <c r="G41" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="s">
+        <v>239</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
@@ -1623,10 +2027,13 @@
       <c r="D42" s="2" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>42</v>
+      <c r="G42" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="s">
+        <v>240</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
@@ -1637,10 +2044,13 @@
       <c r="D43" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>43</v>
+      <c r="G43" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="B44" t="s">
         <v>7</v>
@@ -1651,10 +2061,13 @@
       <c r="D44" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>44</v>
+      <c r="G44" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="6" t="s">
+        <v>242</v>
       </c>
       <c r="B45" t="s">
         <v>7</v>
@@ -1665,10 +2078,13 @@
       <c r="D45" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>45</v>
+      <c r="G45" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
+        <v>243</v>
       </c>
       <c r="B46" t="s">
         <v>7</v>
@@ -1679,10 +2095,13 @@
       <c r="D46" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>46</v>
+      <c r="G46" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="s">
+        <v>244</v>
       </c>
       <c r="B47" t="s">
         <v>7</v>
@@ -1693,10 +2112,13 @@
       <c r="D47" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>47</v>
+      <c r="G47" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="s">
+        <v>245</v>
       </c>
       <c r="B48" t="s">
         <v>7</v>
@@ -1707,10 +2129,13 @@
       <c r="D48" s="2" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>48</v>
+      <c r="G48" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="B49" t="s">
         <v>7</v>
@@ -1721,10 +2146,13 @@
       <c r="D49" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>49</v>
+      <c r="G49" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="s">
+        <v>247</v>
       </c>
       <c r="B50" t="s">
         <v>7</v>
@@ -1735,10 +2163,13 @@
       <c r="D50" s="2" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>50</v>
+      <c r="G50" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="B51" t="s">
         <v>7</v>
@@ -1749,10 +2180,13 @@
       <c r="D51" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>51</v>
+      <c r="G51" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="6" t="s">
+        <v>249</v>
       </c>
       <c r="B52" t="s">
         <v>8</v>
@@ -1763,10 +2197,13 @@
       <c r="D52" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>52</v>
+      <c r="G52" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="6" t="s">
+        <v>203</v>
       </c>
       <c r="B53" t="s">
         <v>8</v>
@@ -1777,10 +2214,13 @@
       <c r="D53" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>53</v>
+      <c r="G53" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="s">
+        <v>250</v>
       </c>
       <c r="B54" t="s">
         <v>8</v>
@@ -1791,10 +2231,13 @@
       <c r="D54" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>54</v>
+      <c r="G54" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="B55" t="s">
         <v>8</v>
@@ -1805,10 +2248,13 @@
       <c r="D55" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>55</v>
+      <c r="G55" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="6" t="s">
+        <v>252</v>
       </c>
       <c r="B56" t="s">
         <v>8</v>
@@ -1819,10 +2265,13 @@
       <c r="D56" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>56</v>
+      <c r="G56" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="B57" t="s">
         <v>9</v>
@@ -1833,10 +2282,13 @@
       <c r="D57" s="2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>57</v>
+      <c r="G57" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="B58" t="s">
         <v>9</v>
@@ -1847,10 +2299,13 @@
       <c r="D58" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>58</v>
+      <c r="G58" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
@@ -1861,10 +2316,13 @@
       <c r="D59" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>59</v>
+      <c r="G59" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="B60" t="s">
         <v>9</v>
@@ -1875,10 +2333,13 @@
       <c r="D60" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>60</v>
+      <c r="G60" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="6" t="s">
+        <v>257</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
@@ -1889,10 +2350,13 @@
       <c r="D61" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>61</v>
+      <c r="G61" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="6" t="s">
+        <v>258</v>
       </c>
       <c r="B62" t="s">
         <v>10</v>
@@ -1903,10 +2367,13 @@
       <c r="D62" s="2" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>62</v>
+      <c r="G62" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="B63" t="s">
         <v>10</v>
@@ -1917,10 +2384,13 @@
       <c r="D63" s="2" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>63</v>
+      <c r="G63" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="6" t="s">
+        <v>260</v>
       </c>
       <c r="B64" t="s">
         <v>10</v>
@@ -1931,10 +2401,13 @@
       <c r="D64" s="2" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>64</v>
+      <c r="G64" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="6" t="s">
+        <v>261</v>
       </c>
       <c r="B65" t="s">
         <v>10</v>
@@ -1945,10 +2418,13 @@
       <c r="D65" s="2" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>65</v>
+      <c r="G65" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
+        <v>262</v>
       </c>
       <c r="B66" t="s">
         <v>10</v>
@@ -1959,10 +2435,13 @@
       <c r="D66" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>66</v>
+      <c r="G66" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
+        <v>263</v>
       </c>
       <c r="B67" t="s">
         <v>11</v>
@@ -1973,10 +2452,13 @@
       <c r="D67" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>67</v>
+      <c r="G67" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="6" t="s">
+        <v>264</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
@@ -1987,10 +2469,13 @@
       <c r="D68" s="2" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>68</v>
+      <c r="G68" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="s">
+        <v>265</v>
       </c>
       <c r="B69" t="s">
         <v>11</v>
@@ -2001,10 +2486,13 @@
       <c r="D69" s="2" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>69</v>
+      <c r="G69" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
+        <v>266</v>
       </c>
       <c r="B70" t="s">
         <v>11</v>
@@ -2015,10 +2503,13 @@
       <c r="D70" s="2" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>70</v>
+      <c r="G70" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
@@ -2029,10 +2520,13 @@
       <c r="D71" s="2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>71</v>
+      <c r="G71" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
+        <v>268</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
@@ -2043,10 +2537,13 @@
       <c r="D72" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>72</v>
+      <c r="G72" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="6" t="s">
+        <v>269</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
@@ -2057,10 +2554,13 @@
       <c r="D73" s="2" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>73</v>
+      <c r="G73" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="B74" t="s">
         <v>11</v>
@@ -2071,10 +2571,13 @@
       <c r="D74" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>74</v>
+      <c r="G74" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="B75" t="s">
         <v>11</v>
@@ -2085,10 +2588,13 @@
       <c r="D75" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>75</v>
+      <c r="G75" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="6" t="s">
+        <v>249</v>
       </c>
       <c r="B76" t="s">
         <v>11</v>
@@ -2099,10 +2605,13 @@
       <c r="D76" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>76</v>
+      <c r="G76" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="6" t="s">
+        <v>272</v>
       </c>
       <c r="B77" t="s">
         <v>11</v>
@@ -2113,10 +2622,13 @@
       <c r="D77" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>77</v>
+      <c r="G77" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="6" t="s">
+        <v>273</v>
       </c>
       <c r="B78" t="s">
         <v>11</v>
@@ -2127,10 +2639,13 @@
       <c r="D78" s="2" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>78</v>
+      <c r="G78" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="B79" t="s">
         <v>11</v>
@@ -2141,10 +2656,13 @@
       <c r="D79" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>79</v>
+      <c r="G79" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="6" t="s">
+        <v>217</v>
       </c>
       <c r="B80" t="s">
         <v>11</v>
@@ -2155,10 +2673,13 @@
       <c r="D80" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <v>80</v>
+      <c r="G80" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="6" t="s">
+        <v>216</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
@@ -2169,10 +2690,13 @@
       <c r="D81" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <v>81</v>
+      <c r="G81" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="B82" t="s">
         <v>12</v>
@@ -2183,10 +2707,13 @@
       <c r="D82" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83">
-        <v>82</v>
+      <c r="G82" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="B83" t="s">
         <v>12</v>
@@ -2197,10 +2724,13 @@
       <c r="D83" s="2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84">
-        <v>83</v>
+      <c r="G83" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="6" t="s">
+        <v>250</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
@@ -2211,10 +2741,13 @@
       <c r="D84" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85">
-        <v>84</v>
+      <c r="G84" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
@@ -2225,10 +2758,13 @@
       <c r="D85" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86">
-        <v>85</v>
+      <c r="G85" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="6" t="s">
+        <v>252</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
@@ -2239,10 +2775,13 @@
       <c r="D86" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <v>86</v>
+      <c r="G86" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="6" t="s">
+        <v>276</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -2253,10 +2792,13 @@
       <c r="D87" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>87</v>
+      <c r="G87" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="6" t="s">
+        <v>277</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -2267,10 +2809,13 @@
       <c r="D88" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89">
-        <v>88</v>
+      <c r="G88" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="6" t="s">
+        <v>278</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -2281,10 +2826,13 @@
       <c r="D89" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90">
-        <v>89</v>
+      <c r="G89" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="6" t="s">
+        <v>279</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -2295,10 +2843,13 @@
       <c r="D90" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91">
-        <v>90</v>
+      <c r="G90" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="6" t="s">
+        <v>280</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -2309,10 +2860,13 @@
       <c r="D91" s="2" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92">
-        <v>91</v>
+      <c r="G91" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="6" t="s">
+        <v>281</v>
       </c>
       <c r="B92" t="s">
         <v>14</v>
@@ -2323,10 +2877,13 @@
       <c r="D92" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93">
-        <v>92</v>
+      <c r="G92" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="6" t="s">
+        <v>282</v>
       </c>
       <c r="B93" t="s">
         <v>14</v>
@@ -2337,10 +2894,13 @@
       <c r="D93" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94">
-        <v>93</v>
+      <c r="G93" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="6" t="s">
+        <v>283</v>
       </c>
       <c r="B94" t="s">
         <v>14</v>
@@ -2351,10 +2911,13 @@
       <c r="D94" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95">
-        <v>94</v>
+      <c r="G94" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="6" t="s">
+        <v>201</v>
       </c>
       <c r="B95" t="s">
         <v>14</v>
@@ -2365,10 +2928,13 @@
       <c r="D95" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96">
-        <v>95</v>
+      <c r="G95" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="B96" t="s">
         <v>14</v>
@@ -2379,10 +2945,13 @@
       <c r="D96" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97">
-        <v>96</v>
+      <c r="G96" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="6" t="s">
+        <v>284</v>
       </c>
       <c r="B97" t="s">
         <v>15</v>
@@ -2393,10 +2962,13 @@
       <c r="D97" s="2" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98">
-        <v>97</v>
+      <c r="G97" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="6" t="s">
+        <v>285</v>
       </c>
       <c r="B98" t="s">
         <v>15</v>
@@ -2407,10 +2979,13 @@
       <c r="D98" s="2" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99">
-        <v>98</v>
+      <c r="G98" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="6" t="s">
+        <v>286</v>
       </c>
       <c r="B99" t="s">
         <v>15</v>
@@ -2421,10 +2996,13 @@
       <c r="D99" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100">
-        <v>99</v>
+      <c r="G99" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="6" t="s">
+        <v>287</v>
       </c>
       <c r="B100" t="s">
         <v>15</v>
@@ -2435,10 +3013,13 @@
       <c r="D100" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101">
-        <v>100</v>
+      <c r="G100" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="6" t="s">
+        <v>288</v>
       </c>
       <c r="B101" t="s">
         <v>15</v>
@@ -2448,6 +3029,9 @@
       </c>
       <c r="D101" s="2" t="s">
         <v>195</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>

--- a/100_easy_leetcode.xlsx
+++ b/100_easy_leetcode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vises\OneDrive\Desktop\Python_programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4783FA1B-9AB4-4751-B82E-E4221452F336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A141657-EF78-4DFD-8073-C557717208EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="294">
   <si>
     <t>No.</t>
   </si>
@@ -893,6 +893,15 @@
   </si>
   <si>
     <t>EASY</t>
+  </si>
+  <si>
+    <t>https://leetcode.com/problems/power-of-three</t>
+  </si>
+  <si>
+    <t>LC326</t>
+  </si>
+  <si>
+    <t>Power of Three</t>
   </si>
 </sst>
 </file>
@@ -973,7 +982,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -982,11 +991,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1292,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.44140625" bestFit="1" customWidth="1"/>
@@ -1321,12 +1325,12 @@
       <c r="F1" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" t="s">
         <v>199</v>
       </c>
       <c r="B2" t="s">
@@ -1346,7 +1350,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" t="s">
         <v>200</v>
       </c>
       <c r="B3" t="s">
@@ -1361,12 +1365,12 @@
       <c r="E3" t="s">
         <v>198</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" t="s">
         <v>201</v>
       </c>
       <c r="B4" t="s">
@@ -1381,12 +1385,12 @@
       <c r="E4" t="s">
         <v>198</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" t="s">
         <v>202</v>
       </c>
       <c r="B5" t="s">
@@ -1398,12 +1402,15 @@
       <c r="D5" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="E5" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" t="s">
         <v>203</v>
       </c>
       <c r="B6" t="s">
@@ -1415,12 +1422,12 @@
       <c r="D6" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" t="s">
         <v>204</v>
       </c>
       <c r="B7" t="s">
@@ -1432,12 +1439,12 @@
       <c r="D7" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" t="s">
         <v>205</v>
       </c>
       <c r="B8" t="s">
@@ -1449,12 +1456,12 @@
       <c r="D8" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" t="s">
         <v>206</v>
       </c>
       <c r="B9" t="s">
@@ -1466,12 +1473,12 @@
       <c r="D9" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" t="s">
         <v>207</v>
       </c>
       <c r="B10" t="s">
@@ -1483,12 +1490,12 @@
       <c r="D10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" t="s">
         <v>208</v>
       </c>
       <c r="B11" t="s">
@@ -1500,12 +1507,12 @@
       <c r="D11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" t="s">
         <v>209</v>
       </c>
       <c r="B12" t="s">
@@ -1517,12 +1524,12 @@
       <c r="D12" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" t="s">
         <v>210</v>
       </c>
       <c r="B13" t="s">
@@ -1534,12 +1541,12 @@
       <c r="D13" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" t="s">
         <v>211</v>
       </c>
       <c r="B14" t="s">
@@ -1551,12 +1558,12 @@
       <c r="D14" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" t="s">
         <v>212</v>
       </c>
       <c r="B15" t="s">
@@ -1568,12 +1575,12 @@
       <c r="D15" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" t="s">
         <v>213</v>
       </c>
       <c r="B16" t="s">
@@ -1585,12 +1592,12 @@
       <c r="D16" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" t="s">
         <v>214</v>
       </c>
       <c r="B17" t="s">
@@ -1602,12 +1609,12 @@
       <c r="D17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" t="s">
         <v>215</v>
       </c>
       <c r="B18" t="s">
@@ -1619,12 +1626,12 @@
       <c r="D18" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" t="s">
         <v>216</v>
       </c>
       <c r="B19" t="s">
@@ -1636,12 +1643,12 @@
       <c r="D19" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" t="s">
         <v>217</v>
       </c>
       <c r="B20" t="s">
@@ -1653,12 +1660,12 @@
       <c r="D20" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" t="s">
         <v>218</v>
       </c>
       <c r="B21" t="s">
@@ -1670,12 +1677,12 @@
       <c r="D21" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" t="s">
         <v>219</v>
       </c>
       <c r="B22" t="s">
@@ -1687,12 +1694,12 @@
       <c r="D22" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" t="s">
         <v>220</v>
       </c>
       <c r="B23" t="s">
@@ -1704,12 +1711,12 @@
       <c r="D23" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" t="s">
         <v>221</v>
       </c>
       <c r="B24" t="s">
@@ -1721,12 +1728,12 @@
       <c r="D24" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" t="s">
         <v>222</v>
       </c>
       <c r="B25" t="s">
@@ -1738,12 +1745,12 @@
       <c r="D25" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" t="s">
         <v>223</v>
       </c>
       <c r="B26" t="s">
@@ -1755,12 +1762,12 @@
       <c r="D26" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" t="s">
         <v>224</v>
       </c>
       <c r="B27" t="s">
@@ -1772,12 +1779,12 @@
       <c r="D27" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
+      <c r="A28" t="s">
         <v>225</v>
       </c>
       <c r="B28" t="s">
@@ -1789,12 +1796,12 @@
       <c r="D28" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
+      <c r="A29" t="s">
         <v>226</v>
       </c>
       <c r="B29" t="s">
@@ -1806,12 +1813,12 @@
       <c r="D29" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" t="s">
         <v>227</v>
       </c>
       <c r="B30" t="s">
@@ -1823,12 +1830,12 @@
       <c r="D30" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="A31" t="s">
         <v>228</v>
       </c>
       <c r="B31" t="s">
@@ -1840,7 +1847,7 @@
       <c r="D31" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" t="s">
         <v>290</v>
       </c>
     </row>
@@ -1857,7 +1864,7 @@
       <c r="D32" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" t="s">
         <v>290</v>
       </c>
     </row>
@@ -1874,7 +1881,7 @@
       <c r="D33" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" t="s">
         <v>290</v>
       </c>
     </row>
@@ -1891,7 +1898,7 @@
       <c r="D34" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" t="s">
         <v>290</v>
       </c>
     </row>
@@ -1908,7 +1915,7 @@
       <c r="D35" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" t="s">
         <v>290</v>
       </c>
     </row>
@@ -1925,12 +1932,12 @@
       <c r="D36" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
+      <c r="A37" t="s">
         <v>234</v>
       </c>
       <c r="B37" t="s">
@@ -1942,12 +1949,12 @@
       <c r="D37" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="G37" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
+      <c r="A38" t="s">
         <v>235</v>
       </c>
       <c r="B38" t="s">
@@ -1959,12 +1966,12 @@
       <c r="D38" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
+      <c r="A39" t="s">
         <v>236</v>
       </c>
       <c r="B39" t="s">
@@ -1976,12 +1983,12 @@
       <c r="D39" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
+      <c r="A40" t="s">
         <v>237</v>
       </c>
       <c r="B40" t="s">
@@ -1993,12 +2000,12 @@
       <c r="D40" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
+      <c r="A41" t="s">
         <v>238</v>
       </c>
       <c r="B41" t="s">
@@ -2010,12 +2017,12 @@
       <c r="D41" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
+      <c r="A42" t="s">
         <v>239</v>
       </c>
       <c r="B42" t="s">
@@ -2027,12 +2034,12 @@
       <c r="D42" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
+      <c r="A43" t="s">
         <v>240</v>
       </c>
       <c r="B43" t="s">
@@ -2044,12 +2051,12 @@
       <c r="D43" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="G43" s="6" t="s">
+      <c r="G43" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
+      <c r="A44" t="s">
         <v>241</v>
       </c>
       <c r="B44" t="s">
@@ -2061,12 +2068,12 @@
       <c r="D44" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
+      <c r="A45" t="s">
         <v>242</v>
       </c>
       <c r="B45" t="s">
@@ -2078,12 +2085,12 @@
       <c r="D45" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G45" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
+      <c r="A46" t="s">
         <v>243</v>
       </c>
       <c r="B46" t="s">
@@ -2095,12 +2102,12 @@
       <c r="D46" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
+      <c r="A47" t="s">
         <v>244</v>
       </c>
       <c r="B47" t="s">
@@ -2112,12 +2119,12 @@
       <c r="D47" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G47" s="6" t="s">
+      <c r="G47" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
+      <c r="A48" t="s">
         <v>245</v>
       </c>
       <c r="B48" t="s">
@@ -2129,12 +2136,12 @@
       <c r="D48" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G48" s="6" t="s">
+      <c r="G48" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
+      <c r="A49" t="s">
         <v>246</v>
       </c>
       <c r="B49" t="s">
@@ -2146,12 +2153,12 @@
       <c r="D49" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G49" s="6" t="s">
+      <c r="G49" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
+      <c r="A50" t="s">
         <v>247</v>
       </c>
       <c r="B50" t="s">
@@ -2163,12 +2170,12 @@
       <c r="D50" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="G50" s="6" t="s">
+      <c r="G50" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
+      <c r="A51" t="s">
         <v>248</v>
       </c>
       <c r="B51" t="s">
@@ -2180,12 +2187,12 @@
       <c r="D51" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G51" s="6" t="s">
+      <c r="G51" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
+      <c r="A52" t="s">
         <v>249</v>
       </c>
       <c r="B52" t="s">
@@ -2197,12 +2204,12 @@
       <c r="D52" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="G52" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
+      <c r="A53" t="s">
         <v>203</v>
       </c>
       <c r="B53" t="s">
@@ -2214,12 +2221,12 @@
       <c r="D53" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="G53" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
+      <c r="A54" t="s">
         <v>250</v>
       </c>
       <c r="B54" t="s">
@@ -2231,806 +2238,849 @@
       <c r="D54" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="G54" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
-        <v>251</v>
+      <c r="A55" t="s">
+        <v>254</v>
       </c>
       <c r="B55" t="s">
         <v>8</v>
       </c>
       <c r="C55" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G55" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E55" t="s">
+        <v>198</v>
+      </c>
+      <c r="G55" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
-        <v>252</v>
+      <c r="A56" t="s">
+        <v>292</v>
       </c>
       <c r="B56" t="s">
         <v>8</v>
       </c>
       <c r="C56" t="s">
+        <v>293</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E56" t="s">
+        <v>198</v>
+      </c>
+      <c r="G56" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>251</v>
+      </c>
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" t="s">
+        <v>198</v>
+      </c>
+      <c r="G57" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>252</v>
+      </c>
+      <c r="B58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" t="s">
         <v>69</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
+      <c r="G58" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
         <v>253</v>
-      </c>
-      <c r="B57" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" t="s">
-        <v>70</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="B58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" t="s">
-        <v>71</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="B59" t="s">
         <v>9</v>
       </c>
       <c r="C59" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G59" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G59" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
-        <v>256</v>
+      <c r="A60" t="s">
+        <v>254</v>
       </c>
       <c r="B60" t="s">
         <v>9</v>
       </c>
       <c r="C60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="G60" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="G60" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>257</v>
+      <c r="A61" t="s">
+        <v>255</v>
       </c>
       <c r="B61" t="s">
         <v>9</v>
       </c>
       <c r="C61" t="s">
+        <v>72</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G61" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>256</v>
+      </c>
+      <c r="B62" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>73</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G62" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>257</v>
+      </c>
+      <c r="B63" t="s">
+        <v>9</v>
+      </c>
+      <c r="C63" t="s">
         <v>74</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="G61" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
+      <c r="G63" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
         <v>258</v>
-      </c>
-      <c r="B62" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" t="s">
-        <v>75</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B63" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" t="s">
-        <v>76</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
-        <v>260</v>
       </c>
       <c r="B64" t="s">
         <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G64" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G64" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
-        <v>261</v>
+      <c r="A65" t="s">
+        <v>259</v>
       </c>
       <c r="B65" t="s">
         <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G65" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="G65" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
-        <v>262</v>
+      <c r="A66" t="s">
+        <v>260</v>
       </c>
       <c r="B66" t="s">
         <v>10</v>
       </c>
       <c r="C66" t="s">
+        <v>77</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G66" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>261</v>
+      </c>
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>78</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G67" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>262</v>
+      </c>
+      <c r="B68" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" t="s">
         <v>79</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D68" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="G66" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
+      <c r="G68" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
         <v>263</v>
-      </c>
-      <c r="B67" t="s">
-        <v>11</v>
-      </c>
-      <c r="C67" t="s">
-        <v>80</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="B68" t="s">
-        <v>11</v>
-      </c>
-      <c r="C68" t="s">
-        <v>81</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="B69" t="s">
         <v>11</v>
       </c>
       <c r="C69" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="G69" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="G69" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
-        <v>266</v>
+      <c r="A70" t="s">
+        <v>264</v>
       </c>
       <c r="B70" t="s">
         <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G70" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="G70" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
-        <v>267</v>
+      <c r="A71" t="s">
+        <v>265</v>
       </c>
       <c r="B71" t="s">
         <v>11</v>
       </c>
       <c r="C71" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="G71" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G71" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="s">
-        <v>268</v>
+      <c r="A72" t="s">
+        <v>266</v>
       </c>
       <c r="B72" t="s">
         <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="G72" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G72" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="s">
-        <v>269</v>
+      <c r="A73" t="s">
+        <v>267</v>
       </c>
       <c r="B73" t="s">
         <v>11</v>
       </c>
       <c r="C73" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G73" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G73" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
-        <v>270</v>
+      <c r="A74" t="s">
+        <v>268</v>
       </c>
       <c r="B74" t="s">
         <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G74" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="s">
-        <v>271</v>
+      <c r="A75" t="s">
+        <v>269</v>
       </c>
       <c r="B75" t="s">
         <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="G75" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="G75" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="s">
-        <v>249</v>
+      <c r="A76" t="s">
+        <v>270</v>
       </c>
       <c r="B76" t="s">
         <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G76" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="G76" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
-        <v>272</v>
+      <c r="A77" t="s">
+        <v>271</v>
       </c>
       <c r="B77" t="s">
         <v>11</v>
       </c>
       <c r="C77" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G77" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="G77" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
-        <v>273</v>
+      <c r="A78" t="s">
+        <v>249</v>
       </c>
       <c r="B78" t="s">
         <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="G78" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G78" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" s="6" t="s">
-        <v>218</v>
+      <c r="A79" t="s">
+        <v>272</v>
       </c>
       <c r="B79" t="s">
         <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G79" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G79" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
-        <v>217</v>
+      <c r="A80" t="s">
+        <v>273</v>
       </c>
       <c r="B80" t="s">
         <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G80" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G80" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
-        <v>216</v>
+      <c r="A81" t="s">
+        <v>218</v>
       </c>
       <c r="B81" t="s">
         <v>11</v>
       </c>
       <c r="C81" t="s">
+        <v>35</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G81" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>217</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" t="s">
+        <v>34</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G82" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>216</v>
+      </c>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
         <v>33</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D83" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G81" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
+      <c r="G83" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
         <v>274</v>
-      </c>
-      <c r="B82" t="s">
-        <v>12</v>
-      </c>
-      <c r="C82" t="s">
-        <v>91</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="B83" t="s">
-        <v>12</v>
-      </c>
-      <c r="C83" t="s">
-        <v>92</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G83" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="B84" t="s">
         <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G84" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="G84" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
-        <v>251</v>
+      <c r="A85" t="s">
+        <v>275</v>
       </c>
       <c r="B85" t="s">
         <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G85" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="G85" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
-        <v>252</v>
+      <c r="A86" t="s">
+        <v>250</v>
       </c>
       <c r="B86" t="s">
         <v>12</v>
       </c>
       <c r="C86" t="s">
+        <v>67</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G86" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>251</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G87" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>252</v>
+      </c>
+      <c r="B88" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
         <v>69</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G86" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
+      <c r="G88" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
         <v>276</v>
-      </c>
-      <c r="B87" t="s">
-        <v>13</v>
-      </c>
-      <c r="C87" t="s">
-        <v>93</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G87" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="B88" t="s">
-        <v>13</v>
-      </c>
-      <c r="C88" t="s">
-        <v>94</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
-        <v>278</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G89" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G89" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
-        <v>279</v>
+      <c r="A90" t="s">
+        <v>277</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
       </c>
       <c r="C90" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G90" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="G90" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
-        <v>280</v>
+      <c r="A91" t="s">
+        <v>278</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
       </c>
       <c r="C91" t="s">
+        <v>95</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G91" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>279</v>
+      </c>
+      <c r="B92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" t="s">
+        <v>96</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G92" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>280</v>
+      </c>
+      <c r="B93" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" t="s">
         <v>97</v>
       </c>
-      <c r="D91" s="2" t="s">
+      <c r="D93" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="G91" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="s">
+      <c r="G93" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
         <v>281</v>
-      </c>
-      <c r="B92" t="s">
-        <v>14</v>
-      </c>
-      <c r="C92" t="s">
-        <v>98</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="B93" t="s">
-        <v>14</v>
-      </c>
-      <c r="C93" t="s">
-        <v>99</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="s">
-        <v>283</v>
       </c>
       <c r="B94" t="s">
         <v>14</v>
       </c>
       <c r="C94" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G94" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G94" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" s="6" t="s">
-        <v>201</v>
+      <c r="A95" t="s">
+        <v>282</v>
       </c>
       <c r="B95" t="s">
         <v>14</v>
       </c>
       <c r="C95" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G95" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="G95" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="6" t="s">
-        <v>206</v>
+      <c r="A96" t="s">
+        <v>283</v>
       </c>
       <c r="B96" t="s">
         <v>14</v>
       </c>
       <c r="C96" t="s">
+        <v>100</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G96" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>201</v>
+      </c>
+      <c r="B97" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97" t="s">
+        <v>18</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G97" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>206</v>
+      </c>
+      <c r="B98" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" t="s">
         <v>23</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D98" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G96" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="6" t="s">
+      <c r="G98" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
         <v>284</v>
-      </c>
-      <c r="B97" t="s">
-        <v>15</v>
-      </c>
-      <c r="C97" t="s">
-        <v>101</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G97" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B98" t="s">
-        <v>15</v>
-      </c>
-      <c r="C98" t="s">
-        <v>102</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="G98" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="B99" t="s">
         <v>15</v>
       </c>
       <c r="C99" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G99" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="G99" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" s="6" t="s">
-        <v>287</v>
+      <c r="A100" t="s">
+        <v>285</v>
       </c>
       <c r="B100" t="s">
         <v>15</v>
       </c>
       <c r="C100" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G100" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="G100" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="6" t="s">
-        <v>288</v>
+      <c r="A101" t="s">
+        <v>286</v>
       </c>
       <c r="B101" t="s">
         <v>15</v>
       </c>
       <c r="C101" t="s">
+        <v>103</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G101" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>287</v>
+      </c>
+      <c r="B102" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G102" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>288</v>
+      </c>
+      <c r="B103" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" t="s">
         <v>105</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D103" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G101" s="6" t="s">
+      <c r="G103" t="s">
         <v>290</v>
       </c>
     </row>
@@ -3089,53 +3139,55 @@
     <hyperlink ref="D52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
     <hyperlink ref="D53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
     <hyperlink ref="D54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="D55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="D56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="D57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="D58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="D59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="D60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="D61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="D62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="D63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="D64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="D65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="D66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="D68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="D69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="D70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="D71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="D72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="D73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="D74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="D75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="D76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="D77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="D78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="D79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="D80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="D81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="D82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="D83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="D84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="D85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="D86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
-    <hyperlink ref="D87" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
-    <hyperlink ref="D88" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
-    <hyperlink ref="D89" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
-    <hyperlink ref="D90" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
-    <hyperlink ref="D91" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
-    <hyperlink ref="D92" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
-    <hyperlink ref="D93" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
-    <hyperlink ref="D94" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
-    <hyperlink ref="D95" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
-    <hyperlink ref="D96" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
-    <hyperlink ref="D97" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
-    <hyperlink ref="D98" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
-    <hyperlink ref="D99" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
-    <hyperlink ref="D100" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
-    <hyperlink ref="D101" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D57" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="D58" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
+    <hyperlink ref="D59" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
+    <hyperlink ref="D60" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
+    <hyperlink ref="D61" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
+    <hyperlink ref="D62" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
+    <hyperlink ref="D63" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
+    <hyperlink ref="D64" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
+    <hyperlink ref="D65" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
+    <hyperlink ref="D66" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
+    <hyperlink ref="D67" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="D68" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
+    <hyperlink ref="D69" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
+    <hyperlink ref="D70" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
+    <hyperlink ref="D71" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
+    <hyperlink ref="D72" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="D73" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
+    <hyperlink ref="D74" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
+    <hyperlink ref="D75" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="D76" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
+    <hyperlink ref="D77" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
+    <hyperlink ref="D78" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
+    <hyperlink ref="D79" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
+    <hyperlink ref="D80" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
+    <hyperlink ref="D81" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
+    <hyperlink ref="D82" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
+    <hyperlink ref="D83" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
+    <hyperlink ref="D84" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
+    <hyperlink ref="D85" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
+    <hyperlink ref="D86" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
+    <hyperlink ref="D87" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
+    <hyperlink ref="D88" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="D89" r:id="rId86" xr:uid="{00000000-0004-0000-0000-000055000000}"/>
+    <hyperlink ref="D90" r:id="rId87" xr:uid="{00000000-0004-0000-0000-000056000000}"/>
+    <hyperlink ref="D91" r:id="rId88" xr:uid="{00000000-0004-0000-0000-000057000000}"/>
+    <hyperlink ref="D92" r:id="rId89" xr:uid="{00000000-0004-0000-0000-000058000000}"/>
+    <hyperlink ref="D93" r:id="rId90" xr:uid="{00000000-0004-0000-0000-000059000000}"/>
+    <hyperlink ref="D94" r:id="rId91" xr:uid="{00000000-0004-0000-0000-00005A000000}"/>
+    <hyperlink ref="D95" r:id="rId92" xr:uid="{00000000-0004-0000-0000-00005B000000}"/>
+    <hyperlink ref="D96" r:id="rId93" xr:uid="{00000000-0004-0000-0000-00005C000000}"/>
+    <hyperlink ref="D97" r:id="rId94" xr:uid="{00000000-0004-0000-0000-00005D000000}"/>
+    <hyperlink ref="D98" r:id="rId95" xr:uid="{00000000-0004-0000-0000-00005E000000}"/>
+    <hyperlink ref="D99" r:id="rId96" xr:uid="{00000000-0004-0000-0000-00005F000000}"/>
+    <hyperlink ref="D100" r:id="rId97" xr:uid="{00000000-0004-0000-0000-000060000000}"/>
+    <hyperlink ref="D101" r:id="rId98" xr:uid="{00000000-0004-0000-0000-000061000000}"/>
+    <hyperlink ref="D102" r:id="rId99" xr:uid="{00000000-0004-0000-0000-000062000000}"/>
+    <hyperlink ref="D103" r:id="rId100" xr:uid="{00000000-0004-0000-0000-000063000000}"/>
+    <hyperlink ref="D55" r:id="rId101" xr:uid="{E2D3B9A0-D8C6-4619-A0FC-1A37D6FE63BD}"/>
+    <hyperlink ref="D56" r:id="rId102" xr:uid="{9FED55C3-1441-49F5-9F44-2EAD4211E973}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
